--- a/Test Hardware/KSMT/8730CN/Channel_Assignment_20261027.xlsx
+++ b/Test Hardware/KSMT/8730CN/Channel_Assignment_20261027.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\iTest\homeoffice\Test Hardware\KSMT\8730CN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCEA8F83-F793-4095-846C-BCAFE887269B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D99956F-15F5-4416-B7A6-9D9183E9EEEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LPC" sheetId="6" r:id="rId1"/>
+    <sheet name="Power" sheetId="7" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="896">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="1024">
   <si>
     <t>S2_Lpc_Ch59</t>
   </si>
@@ -2722,19 +2723,408 @@
   </si>
   <si>
     <t>S0_Lpc_A_015</t>
+  </si>
+  <si>
+    <t>S0_DPS_F001</t>
+  </si>
+  <si>
+    <t>S1_DPS_F001</t>
+  </si>
+  <si>
+    <t>S2_DPS_F001</t>
+  </si>
+  <si>
+    <t>S3_DPS_F001</t>
+  </si>
+  <si>
+    <t>S4_DPS_F001</t>
+  </si>
+  <si>
+    <t>S5_DPS_F001</t>
+  </si>
+  <si>
+    <t>S6_DPS_F001</t>
+  </si>
+  <si>
+    <t>S7_DPS_F001</t>
+  </si>
+  <si>
+    <t>S0_DPS_S001</t>
+  </si>
+  <si>
+    <t>S0_DPS_GS001</t>
+  </si>
+  <si>
+    <t>S1_DPS_S001</t>
+  </si>
+  <si>
+    <t>S1_DPS_GS001</t>
+  </si>
+  <si>
+    <t>S2_DPS_S001</t>
+  </si>
+  <si>
+    <t>S2_DPS_GS001</t>
+  </si>
+  <si>
+    <t>S3_DPS_S001</t>
+  </si>
+  <si>
+    <t>S3_DPS_GS001</t>
+  </si>
+  <si>
+    <t>S5_DPS_S001</t>
+  </si>
+  <si>
+    <t>S4_DPS_GS001</t>
+  </si>
+  <si>
+    <t>S4_DPS_S001</t>
+  </si>
+  <si>
+    <t>S5_DPS_GS001</t>
+  </si>
+  <si>
+    <t>S6_DPS_S001</t>
+  </si>
+  <si>
+    <t>S6_DPS_GS001</t>
+  </si>
+  <si>
+    <t>S7_DPS_S001</t>
+  </si>
+  <si>
+    <t>S7_DPS_GS001</t>
+  </si>
+  <si>
+    <t>S23_DPS_F14</t>
+  </si>
+  <si>
+    <t>S23_DPS_F12</t>
+  </si>
+  <si>
+    <t>S23_DPS_F30</t>
+  </si>
+  <si>
+    <t>S23_DPS_F29</t>
+  </si>
+  <si>
+    <t>S24_DPS_F08</t>
+  </si>
+  <si>
+    <t>S24_DPS_F12</t>
+  </si>
+  <si>
+    <t>S24_DPS_F29</t>
+  </si>
+  <si>
+    <t>S24_DPS_F30</t>
+  </si>
+  <si>
+    <t>S24_DPS_F14</t>
+  </si>
+  <si>
+    <t>S0_DPS_F002</t>
+  </si>
+  <si>
+    <t>S0_DPS_S002</t>
+  </si>
+  <si>
+    <t>S0_DPS_GS002</t>
+  </si>
+  <si>
+    <t>S1_DPS_F002</t>
+  </si>
+  <si>
+    <t>S1_DPS_S002</t>
+  </si>
+  <si>
+    <t>S1_DPS_GS002</t>
+  </si>
+  <si>
+    <t>S2_DPS_F002</t>
+  </si>
+  <si>
+    <t>S2_DPS_S002</t>
+  </si>
+  <si>
+    <t>S2_DPS_GS002</t>
+  </si>
+  <si>
+    <t>S3_DPS_F002</t>
+  </si>
+  <si>
+    <t>S3_DPS_S002</t>
+  </si>
+  <si>
+    <t>S3_DPS_GS002</t>
+  </si>
+  <si>
+    <t>S4_DPS_F002</t>
+  </si>
+  <si>
+    <t>S4_DPS_S002</t>
+  </si>
+  <si>
+    <t>S4_DPS_GS002</t>
+  </si>
+  <si>
+    <t>S5_DPS_F002</t>
+  </si>
+  <si>
+    <t>S5_DPS_S002</t>
+  </si>
+  <si>
+    <t>S5_DPS_GS002</t>
+  </si>
+  <si>
+    <t>S6_DPS_F002</t>
+  </si>
+  <si>
+    <t>S6_DPS_S002</t>
+  </si>
+  <si>
+    <t>S6_DPS_GS002</t>
+  </si>
+  <si>
+    <t>S7_DPS_F002</t>
+  </si>
+  <si>
+    <t>S7_DPS_S002</t>
+  </si>
+  <si>
+    <t>S7_DPS_GS002</t>
+  </si>
+  <si>
+    <t>S23_DPS_F11</t>
+  </si>
+  <si>
+    <t>S23_DPS_F09</t>
+  </si>
+  <si>
+    <t>S23_DPS_F26</t>
+  </si>
+  <si>
+    <t>S23_DPS_F27</t>
+  </si>
+  <si>
+    <t>S24_DPS_F11</t>
+  </si>
+  <si>
+    <t>S24_DPS_F09</t>
+  </si>
+  <si>
+    <t>S24_DPS_F27</t>
+  </si>
+  <si>
+    <t>S24_DPS_F26</t>
+  </si>
+  <si>
+    <t>S0_DPS_F004</t>
+  </si>
+  <si>
+    <t>S0_DPS_S004</t>
+  </si>
+  <si>
+    <t>S0_DPS_GS004</t>
+  </si>
+  <si>
+    <t>S1_DPS_F004</t>
+  </si>
+  <si>
+    <t>S1_DPS_S004</t>
+  </si>
+  <si>
+    <t>S1_DPS_GS004</t>
+  </si>
+  <si>
+    <t>S2_DPS_F004</t>
+  </si>
+  <si>
+    <t>S2_DPS_S004</t>
+  </si>
+  <si>
+    <t>S2_DPS_GS004</t>
+  </si>
+  <si>
+    <t>S3_DPS_F004</t>
+  </si>
+  <si>
+    <t>S3_DPS_S004</t>
+  </si>
+  <si>
+    <t>S3_DPS_GS004</t>
+  </si>
+  <si>
+    <t>S4_DPS_F004</t>
+  </si>
+  <si>
+    <t>S4_DPS_S004</t>
+  </si>
+  <si>
+    <t>S4_DPS_GS004</t>
+  </si>
+  <si>
+    <t>S5_DPS_F004</t>
+  </si>
+  <si>
+    <t>S5_DPS_S004</t>
+  </si>
+  <si>
+    <t>S5_DPS_GS004</t>
+  </si>
+  <si>
+    <t>S6_DPS_F004</t>
+  </si>
+  <si>
+    <t>S6_DPS_S004</t>
+  </si>
+  <si>
+    <t>S6_DPS_GS004</t>
+  </si>
+  <si>
+    <t>S7_DPS_F004</t>
+  </si>
+  <si>
+    <t>S7_DPS_S004</t>
+  </si>
+  <si>
+    <t>S7_DPS_GS004</t>
+  </si>
+  <si>
+    <t>S23_DPS_F08</t>
+  </si>
+  <si>
+    <t>S23_DPS_F06</t>
+  </si>
+  <si>
+    <t>S23_DPS_F24</t>
+  </si>
+  <si>
+    <t>S23_DPS_F23</t>
+  </si>
+  <si>
+    <t>S24_DPS_F06</t>
+  </si>
+  <si>
+    <t>S24_DPS_F24</t>
+  </si>
+  <si>
+    <t>S24_DPS_F23</t>
+  </si>
+  <si>
+    <t>S0_DPS_F006</t>
+  </si>
+  <si>
+    <t>S0_DPS_S006</t>
+  </si>
+  <si>
+    <t>S0_DPS_GS006</t>
+  </si>
+  <si>
+    <t>S1_DPS_F006</t>
+  </si>
+  <si>
+    <t>S1_DPS_S006</t>
+  </si>
+  <si>
+    <t>S1_DPS_GS006</t>
+  </si>
+  <si>
+    <t>S2_DPS_F006</t>
+  </si>
+  <si>
+    <t>S2_DPS_S006</t>
+  </si>
+  <si>
+    <t>S2_DPS_GS006</t>
+  </si>
+  <si>
+    <t>S3_DPS_F006</t>
+  </si>
+  <si>
+    <t>S3_DPS_S006</t>
+  </si>
+  <si>
+    <t>S3_DPS_GS006</t>
+  </si>
+  <si>
+    <t>S4_DPS_F006</t>
+  </si>
+  <si>
+    <t>S4_DPS_S006</t>
+  </si>
+  <si>
+    <t>S4_DPS_GS006</t>
+  </si>
+  <si>
+    <t>S5_DPS_F006</t>
+  </si>
+  <si>
+    <t>S5_DPS_S006</t>
+  </si>
+  <si>
+    <t>S5_DPS_GS006</t>
+  </si>
+  <si>
+    <t>S6_DPS_F006</t>
+  </si>
+  <si>
+    <t>S6_DPS_S006</t>
+  </si>
+  <si>
+    <t>S6_DPS_GS006</t>
+  </si>
+  <si>
+    <t>S7_DPS_F006</t>
+  </si>
+  <si>
+    <t>S7_DPS_S006</t>
+  </si>
+  <si>
+    <t>S7_DPS_GS006</t>
+  </si>
+  <si>
+    <t>S23_DPS_F05</t>
+  </si>
+  <si>
+    <t>S23_DPS_F03</t>
+  </si>
+  <si>
+    <t>S23_DPS_F21</t>
+  </si>
+  <si>
+    <t>S23_DPS_F20</t>
+  </si>
+  <si>
+    <t>S24_DPS_F05</t>
+  </si>
+  <si>
+    <t>S24_DPS_F03</t>
+  </si>
+  <si>
+    <t>S24_DPS_F21</t>
+  </si>
+  <si>
+    <t>S24_DPS_F20</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2757,8 +3147,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3040,13 +3434,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7446F8FF-AAE0-433B-B0C4-A625F81C66F3}">
   <dimension ref="A1:B448"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>651</v>
       </c>
@@ -3054,7 +3448,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>652</v>
       </c>
@@ -3062,7 +3456,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>653</v>
       </c>
@@ -3070,7 +3464,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>654</v>
       </c>
@@ -3078,7 +3472,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>655</v>
       </c>
@@ -3086,7 +3480,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>656</v>
       </c>
@@ -3094,7 +3488,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>657</v>
       </c>
@@ -3102,7 +3496,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>658</v>
       </c>
@@ -3110,7 +3504,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>659</v>
       </c>
@@ -3118,7 +3512,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>660</v>
       </c>
@@ -3126,7 +3520,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>661</v>
       </c>
@@ -3134,7 +3528,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>662</v>
       </c>
@@ -3142,7 +3536,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>663</v>
       </c>
@@ -3150,7 +3544,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>664</v>
       </c>
@@ -3158,7 +3552,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>665</v>
       </c>
@@ -3166,7 +3560,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>666</v>
       </c>
@@ -3174,7 +3568,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>667</v>
       </c>
@@ -3182,7 +3576,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>668</v>
       </c>
@@ -3190,7 +3584,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>669</v>
       </c>
@@ -3198,7 +3592,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>670</v>
       </c>
@@ -3206,7 +3600,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
         <v>671</v>
       </c>
@@ -3214,7 +3608,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
         <v>672</v>
       </c>
@@ -3222,7 +3616,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>673</v>
       </c>
@@ -3230,7 +3624,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>674</v>
       </c>
@@ -3238,7 +3632,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>675</v>
       </c>
@@ -3246,7 +3640,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>676</v>
       </c>
@@ -3254,7 +3648,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
         <v>677</v>
       </c>
@@ -3262,7 +3656,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2">
       <c r="A28" t="s">
         <v>678</v>
       </c>
@@ -3270,7 +3664,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2">
       <c r="A29" t="s">
         <v>679</v>
       </c>
@@ -3278,7 +3672,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2">
       <c r="A30" t="s">
         <v>680</v>
       </c>
@@ -3286,7 +3680,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2">
       <c r="A31" t="s">
         <v>681</v>
       </c>
@@ -3294,7 +3688,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2">
       <c r="A32" t="s">
         <v>682</v>
       </c>
@@ -3302,7 +3696,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2">
       <c r="A33" t="s">
         <v>683</v>
       </c>
@@ -3310,7 +3704,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2">
       <c r="A34" t="s">
         <v>684</v>
       </c>
@@ -3318,7 +3712,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2">
       <c r="A35" t="s">
         <v>685</v>
       </c>
@@ -3326,7 +3720,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2">
       <c r="A36" t="s">
         <v>686</v>
       </c>
@@ -3334,7 +3728,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2">
       <c r="A37" t="s">
         <v>687</v>
       </c>
@@ -3342,7 +3736,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2">
       <c r="A38" t="s">
         <v>688</v>
       </c>
@@ -3350,7 +3744,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2">
       <c r="A39" t="s">
         <v>689</v>
       </c>
@@ -3358,7 +3752,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2">
       <c r="A40" t="s">
         <v>690</v>
       </c>
@@ -3366,7 +3760,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2">
       <c r="A41" t="s">
         <v>691</v>
       </c>
@@ -3374,7 +3768,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2">
       <c r="A42" t="s">
         <v>692</v>
       </c>
@@ -3382,7 +3776,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2">
       <c r="A43" t="s">
         <v>693</v>
       </c>
@@ -3390,7 +3784,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2">
       <c r="A44" t="s">
         <v>694</v>
       </c>
@@ -3398,7 +3792,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2">
       <c r="A45" t="s">
         <v>695</v>
       </c>
@@ -3406,7 +3800,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2">
       <c r="A46" t="s">
         <v>696</v>
       </c>
@@ -3414,7 +3808,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2">
       <c r="A47" t="s">
         <v>697</v>
       </c>
@@ -3422,7 +3816,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2">
       <c r="A48" t="s">
         <v>698</v>
       </c>
@@ -3430,7 +3824,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2">
       <c r="A49" t="s">
         <v>699</v>
       </c>
@@ -3438,7 +3832,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2">
       <c r="A50" t="s">
         <v>700</v>
       </c>
@@ -3446,7 +3840,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2">
       <c r="A51" t="s">
         <v>701</v>
       </c>
@@ -3454,7 +3848,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2">
       <c r="A52" t="s">
         <v>702</v>
       </c>
@@ -3462,7 +3856,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2">
       <c r="A53" t="s">
         <v>703</v>
       </c>
@@ -3470,7 +3864,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2">
       <c r="A54" t="s">
         <v>704</v>
       </c>
@@ -3478,7 +3872,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2">
       <c r="A55" t="s">
         <v>705</v>
       </c>
@@ -3486,7 +3880,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2">
       <c r="A56" t="s">
         <v>706</v>
       </c>
@@ -3494,7 +3888,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2">
       <c r="A57" t="s">
         <v>707</v>
       </c>
@@ -3502,7 +3896,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2">
       <c r="A58" t="s">
         <v>708</v>
       </c>
@@ -3510,7 +3904,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2">
       <c r="A59" t="s">
         <v>709</v>
       </c>
@@ -3518,7 +3912,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2">
       <c r="A60" t="s">
         <v>710</v>
       </c>
@@ -3526,7 +3920,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2">
       <c r="A61" t="s">
         <v>711</v>
       </c>
@@ -3534,7 +3928,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2">
       <c r="A62" t="s">
         <v>712</v>
       </c>
@@ -3542,7 +3936,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2">
       <c r="A63" t="s">
         <v>713</v>
       </c>
@@ -3550,7 +3944,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2">
       <c r="A64" t="s">
         <v>714</v>
       </c>
@@ -3558,7 +3952,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2">
       <c r="A65" t="s">
         <v>715</v>
       </c>
@@ -3566,7 +3960,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2">
       <c r="A66" t="s">
         <v>716</v>
       </c>
@@ -3574,7 +3968,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2">
       <c r="A67" t="s">
         <v>717</v>
       </c>
@@ -3582,7 +3976,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2">
       <c r="A68" t="s">
         <v>718</v>
       </c>
@@ -3590,7 +3984,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2">
       <c r="A69" t="s">
         <v>719</v>
       </c>
@@ -3598,7 +3992,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2">
       <c r="A70" t="s">
         <v>720</v>
       </c>
@@ -3606,7 +4000,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2">
       <c r="A71" t="s">
         <v>721</v>
       </c>
@@ -3614,7 +4008,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2">
       <c r="A72" t="s">
         <v>722</v>
       </c>
@@ -3622,7 +4016,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2">
       <c r="A73" t="s">
         <v>723</v>
       </c>
@@ -3630,7 +4024,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2">
       <c r="A74" t="s">
         <v>724</v>
       </c>
@@ -3638,7 +4032,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2">
       <c r="A75" t="s">
         <v>725</v>
       </c>
@@ -3646,7 +4040,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2">
       <c r="A76" t="s">
         <v>726</v>
       </c>
@@ -3654,7 +4048,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2">
       <c r="A77" t="s">
         <v>727</v>
       </c>
@@ -3662,7 +4056,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2">
       <c r="A78" t="s">
         <v>728</v>
       </c>
@@ -3670,7 +4064,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2">
       <c r="A79" t="s">
         <v>729</v>
       </c>
@@ -3678,7 +4072,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2">
       <c r="A80" t="s">
         <v>730</v>
       </c>
@@ -3686,7 +4080,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2">
       <c r="A81" t="s">
         <v>731</v>
       </c>
@@ -3694,7 +4088,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2">
       <c r="A82" t="s">
         <v>732</v>
       </c>
@@ -3702,7 +4096,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2">
       <c r="A83" t="s">
         <v>733</v>
       </c>
@@ -3710,7 +4104,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2">
       <c r="A84" t="s">
         <v>734</v>
       </c>
@@ -3718,7 +4112,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2">
       <c r="A85" t="s">
         <v>735</v>
       </c>
@@ -3726,7 +4120,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2">
       <c r="A86" t="s">
         <v>736</v>
       </c>
@@ -3734,7 +4128,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2">
       <c r="A87" t="s">
         <v>737</v>
       </c>
@@ -3742,7 +4136,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2">
       <c r="A88" t="s">
         <v>738</v>
       </c>
@@ -3750,7 +4144,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2">
       <c r="A89" t="s">
         <v>739</v>
       </c>
@@ -3758,7 +4152,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2">
       <c r="A90" t="s">
         <v>740</v>
       </c>
@@ -3766,7 +4160,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2">
       <c r="A91" t="s">
         <v>741</v>
       </c>
@@ -3774,7 +4168,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2">
       <c r="A92" t="s">
         <v>742</v>
       </c>
@@ -3782,7 +4176,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2">
       <c r="A93" t="s">
         <v>743</v>
       </c>
@@ -3790,7 +4184,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2">
       <c r="A94" t="s">
         <v>744</v>
       </c>
@@ -3798,7 +4192,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2">
       <c r="A95" t="s">
         <v>745</v>
       </c>
@@ -3806,7 +4200,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2">
       <c r="A96" t="s">
         <v>746</v>
       </c>
@@ -3814,7 +4208,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2">
       <c r="A97" t="s">
         <v>747</v>
       </c>
@@ -3822,7 +4216,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2">
       <c r="A98" t="s">
         <v>748</v>
       </c>
@@ -3830,7 +4224,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2">
       <c r="A99" t="s">
         <v>749</v>
       </c>
@@ -3838,7 +4232,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2">
       <c r="A100" t="s">
         <v>750</v>
       </c>
@@ -3846,7 +4240,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2">
       <c r="A101" t="s">
         <v>751</v>
       </c>
@@ -3854,7 +4248,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2">
       <c r="A102" t="s">
         <v>752</v>
       </c>
@@ -3862,7 +4256,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2">
       <c r="A103" t="s">
         <v>753</v>
       </c>
@@ -3870,7 +4264,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2">
       <c r="A104" t="s">
         <v>754</v>
       </c>
@@ -3878,7 +4272,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2">
       <c r="A105" t="s">
         <v>755</v>
       </c>
@@ -3886,7 +4280,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2">
       <c r="A106" t="s">
         <v>756</v>
       </c>
@@ -3894,7 +4288,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2">
       <c r="A107" t="s">
         <v>757</v>
       </c>
@@ -3902,7 +4296,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2">
       <c r="A108" t="s">
         <v>758</v>
       </c>
@@ -3910,7 +4304,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2">
       <c r="A109" t="s">
         <v>759</v>
       </c>
@@ -3918,7 +4312,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2">
       <c r="A110" t="s">
         <v>760</v>
       </c>
@@ -3926,7 +4320,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2">
       <c r="A111" t="s">
         <v>761</v>
       </c>
@@ -3934,7 +4328,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2">
       <c r="A112" t="s">
         <v>762</v>
       </c>
@@ -3942,7 +4336,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2">
       <c r="A113" t="s">
         <v>763</v>
       </c>
@@ -3950,7 +4344,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2">
       <c r="A114" t="s">
         <v>764</v>
       </c>
@@ -3958,7 +4352,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2">
       <c r="A115" t="s">
         <v>765</v>
       </c>
@@ -3966,7 +4360,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:2">
       <c r="A116" t="s">
         <v>766</v>
       </c>
@@ -3974,7 +4368,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:2">
       <c r="A117" t="s">
         <v>767</v>
       </c>
@@ -3982,7 +4376,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:2">
       <c r="A118" t="s">
         <v>768</v>
       </c>
@@ -3990,7 +4384,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:2">
       <c r="A119" t="s">
         <v>769</v>
       </c>
@@ -3998,7 +4392,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:2">
       <c r="A120" t="s">
         <v>770</v>
       </c>
@@ -4006,7 +4400,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:2">
       <c r="A121" t="s">
         <v>771</v>
       </c>
@@ -4014,7 +4408,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:2">
       <c r="A122" t="s">
         <v>772</v>
       </c>
@@ -4022,7 +4416,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:2">
       <c r="A123" t="s">
         <v>773</v>
       </c>
@@ -4030,7 +4424,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:2">
       <c r="A124" t="s">
         <v>774</v>
       </c>
@@ -4038,7 +4432,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:2">
       <c r="A125" t="s">
         <v>775</v>
       </c>
@@ -4046,7 +4440,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:2">
       <c r="A126" t="s">
         <v>776</v>
       </c>
@@ -4054,7 +4448,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:2">
       <c r="A127" t="s">
         <v>777</v>
       </c>
@@ -4062,7 +4456,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:2">
       <c r="A128" t="s">
         <v>778</v>
       </c>
@@ -4070,7 +4464,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:2">
       <c r="A129" t="s">
         <v>779</v>
       </c>
@@ -4078,7 +4472,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:2">
       <c r="A130" t="s">
         <v>780</v>
       </c>
@@ -4086,7 +4480,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:2">
       <c r="A131" t="s">
         <v>781</v>
       </c>
@@ -4094,7 +4488,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:2">
       <c r="A132" t="s">
         <v>782</v>
       </c>
@@ -4102,7 +4496,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:2">
       <c r="A133" t="s">
         <v>783</v>
       </c>
@@ -4110,7 +4504,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:2">
       <c r="A134" t="s">
         <v>784</v>
       </c>
@@ -4118,7 +4512,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:2">
       <c r="A135" t="s">
         <v>785</v>
       </c>
@@ -4126,7 +4520,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:2">
       <c r="A136" t="s">
         <v>786</v>
       </c>
@@ -4134,7 +4528,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:2">
       <c r="A137" t="s">
         <v>787</v>
       </c>
@@ -4142,7 +4536,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:2">
       <c r="A138" t="s">
         <v>788</v>
       </c>
@@ -4150,7 +4544,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:2">
       <c r="A139" t="s">
         <v>789</v>
       </c>
@@ -4158,7 +4552,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:2">
       <c r="A140" t="s">
         <v>790</v>
       </c>
@@ -4166,7 +4560,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:2">
       <c r="A141" t="s">
         <v>791</v>
       </c>
@@ -4174,7 +4568,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:2">
       <c r="A142" t="s">
         <v>792</v>
       </c>
@@ -4182,7 +4576,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:2">
       <c r="A143" t="s">
         <v>793</v>
       </c>
@@ -4190,7 +4584,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:2">
       <c r="A144" t="s">
         <v>794</v>
       </c>
@@ -4198,7 +4592,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:2">
       <c r="A145" t="s">
         <v>795</v>
       </c>
@@ -4206,7 +4600,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:2">
       <c r="A146" t="s">
         <v>796</v>
       </c>
@@ -4214,7 +4608,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:2">
       <c r="A147" t="s">
         <v>797</v>
       </c>
@@ -4222,7 +4616,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:2">
       <c r="A148" t="s">
         <v>798</v>
       </c>
@@ -4230,7 +4624,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:2">
       <c r="A149" t="s">
         <v>799</v>
       </c>
@@ -4238,7 +4632,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:2">
       <c r="A150" t="s">
         <v>800</v>
       </c>
@@ -4246,7 +4640,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:2">
       <c r="A151" t="s">
         <v>801</v>
       </c>
@@ -4254,7 +4648,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:2">
       <c r="A152" t="s">
         <v>802</v>
       </c>
@@ -4262,7 +4656,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:2">
       <c r="A153" t="s">
         <v>803</v>
       </c>
@@ -4270,7 +4664,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:2">
       <c r="A154" t="s">
         <v>804</v>
       </c>
@@ -4278,7 +4672,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:2">
       <c r="A155" t="s">
         <v>805</v>
       </c>
@@ -4286,7 +4680,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:2">
       <c r="A156" t="s">
         <v>806</v>
       </c>
@@ -4294,7 +4688,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:2">
       <c r="A157" t="s">
         <v>807</v>
       </c>
@@ -4302,7 +4696,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:2">
       <c r="A158" t="s">
         <v>808</v>
       </c>
@@ -4310,7 +4704,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:2">
       <c r="A159" t="s">
         <v>809</v>
       </c>
@@ -4318,7 +4712,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:2">
       <c r="A160" t="s">
         <v>810</v>
       </c>
@@ -4326,7 +4720,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:2">
       <c r="A161" t="s">
         <v>811</v>
       </c>
@@ -4334,7 +4728,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:2">
       <c r="A162" t="s">
         <v>823</v>
       </c>
@@ -4342,7 +4736,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:2">
       <c r="A163" t="s">
         <v>824</v>
       </c>
@@ -4350,7 +4744,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:2">
       <c r="A164" t="s">
         <v>825</v>
       </c>
@@ -4358,7 +4752,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:2">
       <c r="A165" t="s">
         <v>826</v>
       </c>
@@ -4366,7 +4760,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:2">
       <c r="A166" t="s">
         <v>827</v>
       </c>
@@ -4374,7 +4768,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:2">
       <c r="A167" t="s">
         <v>828</v>
       </c>
@@ -4382,7 +4776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:2">
       <c r="A168" t="s">
         <v>829</v>
       </c>
@@ -4390,7 +4784,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:2">
       <c r="A169" t="s">
         <v>830</v>
       </c>
@@ -4398,7 +4792,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:2">
       <c r="A170" t="s">
         <v>831</v>
       </c>
@@ -4406,7 +4800,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:2">
       <c r="A171" t="s">
         <v>832</v>
       </c>
@@ -4414,7 +4808,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:2">
       <c r="A172" t="s">
         <v>833</v>
       </c>
@@ -4422,7 +4816,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:2">
       <c r="A173" t="s">
         <v>834</v>
       </c>
@@ -4430,7 +4824,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:2">
       <c r="A174" t="s">
         <v>835</v>
       </c>
@@ -4438,7 +4832,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:2">
       <c r="A175" t="s">
         <v>836</v>
       </c>
@@ -4446,7 +4840,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:2">
       <c r="A176" t="s">
         <v>837</v>
       </c>
@@ -4454,7 +4848,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:2">
       <c r="A177" t="s">
         <v>838</v>
       </c>
@@ -4462,7 +4856,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:2">
       <c r="A178" t="s">
         <v>839</v>
       </c>
@@ -4470,7 +4864,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:2">
       <c r="A179" t="s">
         <v>840</v>
       </c>
@@ -4478,7 +4872,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:2">
       <c r="A180" t="s">
         <v>841</v>
       </c>
@@ -4486,7 +4880,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:2">
       <c r="A181" t="s">
         <v>842</v>
       </c>
@@ -4494,7 +4888,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:2">
       <c r="A182" t="s">
         <v>843</v>
       </c>
@@ -4502,7 +4896,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:2">
       <c r="A183" t="s">
         <v>844</v>
       </c>
@@ -4510,7 +4904,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:2">
       <c r="A184" t="s">
         <v>845</v>
       </c>
@@ -4518,7 +4912,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:2">
       <c r="A185" t="s">
         <v>846</v>
       </c>
@@ -4526,7 +4920,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:2">
       <c r="A186" t="s">
         <v>847</v>
       </c>
@@ -4534,7 +4928,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:2">
       <c r="A187" t="s">
         <v>848</v>
       </c>
@@ -4542,7 +4936,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:2">
       <c r="A188" t="s">
         <v>849</v>
       </c>
@@ -4550,7 +4944,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:2">
       <c r="A189" t="s">
         <v>854</v>
       </c>
@@ -4558,7 +4952,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:2">
       <c r="A190" t="s">
         <v>855</v>
       </c>
@@ -4566,7 +4960,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:2">
       <c r="A191" t="s">
         <v>856</v>
       </c>
@@ -4574,7 +4968,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:2">
       <c r="A192" t="s">
         <v>857</v>
       </c>
@@ -4582,7 +4976,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:2">
       <c r="A193" t="s">
         <v>858</v>
       </c>
@@ -4590,7 +4984,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:2">
       <c r="A194" t="s">
         <v>859</v>
       </c>
@@ -4598,7 +4992,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:2">
       <c r="A195" t="s">
         <v>861</v>
       </c>
@@ -4606,7 +5000,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:2">
       <c r="A196" t="s">
         <v>862</v>
       </c>
@@ -4614,7 +5008,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:2">
       <c r="A197" t="s">
         <v>863</v>
       </c>
@@ -4622,7 +5016,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:2">
       <c r="A198" t="s">
         <v>864</v>
       </c>
@@ -4630,7 +5024,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:2">
       <c r="A199" t="s">
         <v>865</v>
       </c>
@@ -4638,7 +5032,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:2">
       <c r="A200" t="s">
         <v>866</v>
       </c>
@@ -4646,7 +5040,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:2">
       <c r="A201" t="s">
         <v>867</v>
       </c>
@@ -4654,7 +5048,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:2">
       <c r="A202" t="s">
         <v>869</v>
       </c>
@@ -4662,7 +5056,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:2">
       <c r="A203" t="s">
         <v>870</v>
       </c>
@@ -4670,7 +5064,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:2">
       <c r="A204" t="s">
         <v>871</v>
       </c>
@@ -4678,7 +5072,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:2">
       <c r="A205" t="s">
         <v>872</v>
       </c>
@@ -4686,7 +5080,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:2">
       <c r="A206" t="s">
         <v>873</v>
       </c>
@@ -4694,7 +5088,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:2">
       <c r="A207" t="s">
         <v>875</v>
       </c>
@@ -4702,7 +5096,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:2">
       <c r="A208" t="s">
         <v>876</v>
       </c>
@@ -4710,7 +5104,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:2">
       <c r="A209" t="s">
         <v>877</v>
       </c>
@@ -4718,7 +5112,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:2">
       <c r="A210" t="s">
         <v>878</v>
       </c>
@@ -4726,7 +5120,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:2">
       <c r="A211" t="s">
         <v>879</v>
       </c>
@@ -4734,7 +5128,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:2">
       <c r="A212" t="s">
         <v>880</v>
       </c>
@@ -4742,7 +5136,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:2">
       <c r="A213" t="s">
         <v>427</v>
       </c>
@@ -4750,7 +5144,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:2">
       <c r="A214" t="s">
         <v>428</v>
       </c>
@@ -4758,7 +5152,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:2">
       <c r="A215" t="s">
         <v>429</v>
       </c>
@@ -4766,7 +5160,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:2">
       <c r="A216" t="s">
         <v>430</v>
       </c>
@@ -4774,7 +5168,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:2">
       <c r="A217" t="s">
         <v>431</v>
       </c>
@@ -4782,7 +5176,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:2">
       <c r="A218" t="s">
         <v>432</v>
       </c>
@@ -4790,7 +5184,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:2">
       <c r="A219" t="s">
         <v>433</v>
       </c>
@@ -4798,7 +5192,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:2">
       <c r="A220" t="s">
         <v>434</v>
       </c>
@@ -4806,7 +5200,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:2">
       <c r="A221" t="s">
         <v>435</v>
       </c>
@@ -4814,7 +5208,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:2">
       <c r="A222" t="s">
         <v>436</v>
       </c>
@@ -4822,7 +5216,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:2">
       <c r="A223" t="s">
         <v>437</v>
       </c>
@@ -4830,7 +5224,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:2">
       <c r="A224" t="s">
         <v>438</v>
       </c>
@@ -4838,7 +5232,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:2">
       <c r="A225" t="s">
         <v>439</v>
       </c>
@@ -4846,7 +5240,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:2">
       <c r="A226" t="s">
         <v>440</v>
       </c>
@@ -4854,7 +5248,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:2">
       <c r="A227" t="s">
         <v>441</v>
       </c>
@@ -4862,7 +5256,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:2">
       <c r="A228" t="s">
         <v>442</v>
       </c>
@@ -4870,7 +5264,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:2">
       <c r="A229" t="s">
         <v>443</v>
       </c>
@@ -4878,7 +5272,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:2">
       <c r="A230" t="s">
         <v>444</v>
       </c>
@@ -4886,7 +5280,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:2">
       <c r="A231" t="s">
         <v>445</v>
       </c>
@@ -4894,7 +5288,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:2">
       <c r="A232" t="s">
         <v>446</v>
       </c>
@@ -4902,7 +5296,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:2">
       <c r="A233" t="s">
         <v>447</v>
       </c>
@@ -4910,7 +5304,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:2">
       <c r="A234" t="s">
         <v>448</v>
       </c>
@@ -4918,7 +5312,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:2">
       <c r="A235" t="s">
         <v>449</v>
       </c>
@@ -4926,7 +5320,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:2">
       <c r="A236" t="s">
         <v>450</v>
       </c>
@@ -4934,7 +5328,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:2">
       <c r="A237" t="s">
         <v>451</v>
       </c>
@@ -4942,7 +5336,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:2">
       <c r="A238" t="s">
         <v>452</v>
       </c>
@@ -4950,7 +5344,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:2">
       <c r="A239" t="s">
         <v>453</v>
       </c>
@@ -4958,7 +5352,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:2">
       <c r="A240" t="s">
         <v>454</v>
       </c>
@@ -4966,7 +5360,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:2">
       <c r="A241" t="s">
         <v>455</v>
       </c>
@@ -4974,7 +5368,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:2">
       <c r="A242" t="s">
         <v>456</v>
       </c>
@@ -4982,7 +5376,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:2">
       <c r="A243" t="s">
         <v>457</v>
       </c>
@@ -4990,7 +5384,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:2">
       <c r="A244" t="s">
         <v>458</v>
       </c>
@@ -4998,7 +5392,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:2">
       <c r="A245" t="s">
         <v>459</v>
       </c>
@@ -5006,7 +5400,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:2">
       <c r="A246" t="s">
         <v>460</v>
       </c>
@@ -5014,7 +5408,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:2">
       <c r="A247" t="s">
         <v>461</v>
       </c>
@@ -5022,7 +5416,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:2">
       <c r="A248" t="s">
         <v>462</v>
       </c>
@@ -5030,7 +5424,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:2">
       <c r="A249" t="s">
         <v>463</v>
       </c>
@@ -5038,7 +5432,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:2">
       <c r="A250" t="s">
         <v>464</v>
       </c>
@@ -5046,7 +5440,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:2">
       <c r="A251" t="s">
         <v>465</v>
       </c>
@@ -5054,7 +5448,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:2">
       <c r="A252" t="s">
         <v>466</v>
       </c>
@@ -5062,7 +5456,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:2">
       <c r="A253" t="s">
         <v>467</v>
       </c>
@@ -5070,7 +5464,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:2">
       <c r="A254" t="s">
         <v>468</v>
       </c>
@@ -5078,7 +5472,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:2">
       <c r="A255" t="s">
         <v>469</v>
       </c>
@@ -5086,7 +5480,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:2">
       <c r="A256" t="s">
         <v>470</v>
       </c>
@@ -5094,7 +5488,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:2">
       <c r="A257" t="s">
         <v>471</v>
       </c>
@@ -5102,7 +5496,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:2">
       <c r="A258" t="s">
         <v>472</v>
       </c>
@@ -5110,7 +5504,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:2">
       <c r="A259" t="s">
         <v>473</v>
       </c>
@@ -5118,7 +5512,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:2">
       <c r="A260" t="s">
         <v>474</v>
       </c>
@@ -5126,7 +5520,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:2">
       <c r="A261" t="s">
         <v>475</v>
       </c>
@@ -5134,7 +5528,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:2">
       <c r="A262" t="s">
         <v>476</v>
       </c>
@@ -5142,7 +5536,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:2">
       <c r="A263" t="s">
         <v>477</v>
       </c>
@@ -5150,7 +5544,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:2">
       <c r="A264" t="s">
         <v>478</v>
       </c>
@@ -5158,7 +5552,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:2">
       <c r="A265" t="s">
         <v>479</v>
       </c>
@@ -5166,7 +5560,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:2">
       <c r="A266" t="s">
         <v>480</v>
       </c>
@@ -5174,7 +5568,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:2">
       <c r="A267" t="s">
         <v>481</v>
       </c>
@@ -5182,7 +5576,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:2">
       <c r="A268" t="s">
         <v>482</v>
       </c>
@@ -5190,7 +5584,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:2">
       <c r="A269" t="s">
         <v>483</v>
       </c>
@@ -5198,7 +5592,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:2">
       <c r="A270" t="s">
         <v>484</v>
       </c>
@@ -5206,7 +5600,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:2">
       <c r="A271" t="s">
         <v>485</v>
       </c>
@@ -5214,7 +5608,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:2">
       <c r="A272" t="s">
         <v>486</v>
       </c>
@@ -5222,7 +5616,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:2">
       <c r="A273" t="s">
         <v>487</v>
       </c>
@@ -5230,7 +5624,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:2">
       <c r="A274" t="s">
         <v>488</v>
       </c>
@@ -5238,7 +5632,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:2">
       <c r="A275" t="s">
         <v>489</v>
       </c>
@@ -5246,7 +5640,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:2">
       <c r="A276" t="s">
         <v>490</v>
       </c>
@@ -5254,7 +5648,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:2">
       <c r="A277" t="s">
         <v>491</v>
       </c>
@@ -5262,7 +5656,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:2">
       <c r="A278" t="s">
         <v>492</v>
       </c>
@@ -5270,7 +5664,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:2">
       <c r="A279" t="s">
         <v>493</v>
       </c>
@@ -5278,7 +5672,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:2">
       <c r="A280" t="s">
         <v>494</v>
       </c>
@@ -5286,7 +5680,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:2">
       <c r="A281" t="s">
         <v>495</v>
       </c>
@@ -5294,7 +5688,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:2">
       <c r="A282" t="s">
         <v>496</v>
       </c>
@@ -5302,7 +5696,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:2">
       <c r="A283" t="s">
         <v>497</v>
       </c>
@@ -5310,7 +5704,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:2">
       <c r="A284" t="s">
         <v>498</v>
       </c>
@@ -5318,7 +5712,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:2">
       <c r="A285" t="s">
         <v>499</v>
       </c>
@@ -5326,7 +5720,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:2">
       <c r="A286" t="s">
         <v>500</v>
       </c>
@@ -5334,7 +5728,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:2">
       <c r="A287" t="s">
         <v>501</v>
       </c>
@@ -5342,7 +5736,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:2">
       <c r="A288" t="s">
         <v>502</v>
       </c>
@@ -5350,7 +5744,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:2">
       <c r="A289" t="s">
         <v>503</v>
       </c>
@@ -5358,7 +5752,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:2">
       <c r="A290" t="s">
         <v>504</v>
       </c>
@@ -5366,7 +5760,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:2">
       <c r="A291" t="s">
         <v>505</v>
       </c>
@@ -5374,7 +5768,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:2">
       <c r="A292" t="s">
         <v>506</v>
       </c>
@@ -5382,7 +5776,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:2">
       <c r="A293" t="s">
         <v>507</v>
       </c>
@@ -5390,7 +5784,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:2">
       <c r="A294" t="s">
         <v>508</v>
       </c>
@@ -5398,7 +5792,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:2">
       <c r="A295" t="s">
         <v>509</v>
       </c>
@@ -5406,7 +5800,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:2">
       <c r="A296" t="s">
         <v>510</v>
       </c>
@@ -5414,7 +5808,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:2">
       <c r="A297" t="s">
         <v>511</v>
       </c>
@@ -5422,7 +5816,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:2">
       <c r="A298" t="s">
         <v>512</v>
       </c>
@@ -5430,7 +5824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:2">
       <c r="A299" t="s">
         <v>513</v>
       </c>
@@ -5438,7 +5832,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:2">
       <c r="A300" t="s">
         <v>514</v>
       </c>
@@ -5446,7 +5840,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:2">
       <c r="A301" t="s">
         <v>515</v>
       </c>
@@ -5454,7 +5848,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:2">
       <c r="A302" t="s">
         <v>516</v>
       </c>
@@ -5462,7 +5856,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:2">
       <c r="A303" t="s">
         <v>517</v>
       </c>
@@ -5470,7 +5864,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:2">
       <c r="A304" t="s">
         <v>518</v>
       </c>
@@ -5478,7 +5872,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:2">
       <c r="A305" t="s">
         <v>519</v>
       </c>
@@ -5486,7 +5880,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:2">
       <c r="A306" t="s">
         <v>520</v>
       </c>
@@ -5494,7 +5888,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:2">
       <c r="A307" t="s">
         <v>521</v>
       </c>
@@ -5502,7 +5896,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:2">
       <c r="A308" t="s">
         <v>522</v>
       </c>
@@ -5510,7 +5904,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:2">
       <c r="A309" t="s">
         <v>523</v>
       </c>
@@ -5518,7 +5912,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:2">
       <c r="A310" t="s">
         <v>524</v>
       </c>
@@ -5526,7 +5920,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:2">
       <c r="A311" t="s">
         <v>525</v>
       </c>
@@ -5534,7 +5928,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:2">
       <c r="A312" t="s">
         <v>526</v>
       </c>
@@ -5542,7 +5936,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:2">
       <c r="A313" t="s">
         <v>527</v>
       </c>
@@ -5550,7 +5944,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:2">
       <c r="A314" t="s">
         <v>528</v>
       </c>
@@ -5558,7 +5952,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:2">
       <c r="A315" t="s">
         <v>529</v>
       </c>
@@ -5566,7 +5960,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:2">
       <c r="A316" t="s">
         <v>530</v>
       </c>
@@ -5574,7 +5968,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:2">
       <c r="A317" t="s">
         <v>531</v>
       </c>
@@ -5582,7 +5976,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:2">
       <c r="A318" t="s">
         <v>532</v>
       </c>
@@ -5590,7 +5984,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:2">
       <c r="A319" t="s">
         <v>533</v>
       </c>
@@ -5598,7 +5992,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:2">
       <c r="A320" t="s">
         <v>534</v>
       </c>
@@ -5606,7 +6000,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:2">
       <c r="A321" t="s">
         <v>535</v>
       </c>
@@ -5614,7 +6008,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:2">
       <c r="A322" t="s">
         <v>536</v>
       </c>
@@ -5622,7 +6016,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:2">
       <c r="A323" t="s">
         <v>537</v>
       </c>
@@ -5630,7 +6024,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:2">
       <c r="A324" t="s">
         <v>538</v>
       </c>
@@ -5638,7 +6032,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:2">
       <c r="A325" t="s">
         <v>539</v>
       </c>
@@ -5646,7 +6040,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:2">
       <c r="A326" t="s">
         <v>540</v>
       </c>
@@ -5654,7 +6048,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:2">
       <c r="A327" t="s">
         <v>541</v>
       </c>
@@ -5662,7 +6056,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:2">
       <c r="A328" t="s">
         <v>542</v>
       </c>
@@ -5670,7 +6064,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:2">
       <c r="A329" t="s">
         <v>543</v>
       </c>
@@ -5678,7 +6072,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:2">
       <c r="A330" t="s">
         <v>544</v>
       </c>
@@ -5686,7 +6080,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:2">
       <c r="A331" t="s">
         <v>545</v>
       </c>
@@ -5694,7 +6088,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:2">
       <c r="A332" t="s">
         <v>546</v>
       </c>
@@ -5702,7 +6096,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:2">
       <c r="A333" t="s">
         <v>547</v>
       </c>
@@ -5710,7 +6104,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:2">
       <c r="A334" t="s">
         <v>548</v>
       </c>
@@ -5718,7 +6112,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:2">
       <c r="A335" t="s">
         <v>549</v>
       </c>
@@ -5726,7 +6120,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:2">
       <c r="A336" t="s">
         <v>550</v>
       </c>
@@ -5734,7 +6128,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:2">
       <c r="A337" t="s">
         <v>551</v>
       </c>
@@ -5742,7 +6136,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:2">
       <c r="A338" t="s">
         <v>552</v>
       </c>
@@ -5750,7 +6144,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:2">
       <c r="A339" t="s">
         <v>553</v>
       </c>
@@ -5758,7 +6152,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:2">
       <c r="A340" t="s">
         <v>554</v>
       </c>
@@ -5766,7 +6160,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:2">
       <c r="A341" t="s">
         <v>555</v>
       </c>
@@ -5774,7 +6168,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:2">
       <c r="A342" t="s">
         <v>556</v>
       </c>
@@ -5782,7 +6176,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:2">
       <c r="A343" t="s">
         <v>557</v>
       </c>
@@ -5790,7 +6184,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:2">
       <c r="A344" t="s">
         <v>558</v>
       </c>
@@ -5798,7 +6192,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:2">
       <c r="A345" t="s">
         <v>559</v>
       </c>
@@ -5806,7 +6200,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:2">
       <c r="A346" t="s">
         <v>560</v>
       </c>
@@ -5814,7 +6208,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:2">
       <c r="A347" t="s">
         <v>561</v>
       </c>
@@ -5822,7 +6216,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:2">
       <c r="A348" t="s">
         <v>562</v>
       </c>
@@ -5830,7 +6224,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:2">
       <c r="A349" t="s">
         <v>563</v>
       </c>
@@ -5838,7 +6232,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:2">
       <c r="A350" t="s">
         <v>564</v>
       </c>
@@ -5846,7 +6240,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:2">
       <c r="A351" t="s">
         <v>565</v>
       </c>
@@ -5854,7 +6248,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="352" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:2">
       <c r="A352" t="s">
         <v>566</v>
       </c>
@@ -5862,7 +6256,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="353" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:2">
       <c r="A353" t="s">
         <v>567</v>
       </c>
@@ -5870,7 +6264,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="354" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:2">
       <c r="A354" t="s">
         <v>568</v>
       </c>
@@ -5878,7 +6272,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="355" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:2">
       <c r="A355" t="s">
         <v>569</v>
       </c>
@@ -5886,7 +6280,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:2">
       <c r="A356" t="s">
         <v>570</v>
       </c>
@@ -5894,7 +6288,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="357" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:2">
       <c r="A357" t="s">
         <v>571</v>
       </c>
@@ -5902,7 +6296,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="358" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:2">
       <c r="A358" t="s">
         <v>572</v>
       </c>
@@ -5910,7 +6304,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="359" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:2">
       <c r="A359" t="s">
         <v>573</v>
       </c>
@@ -5918,7 +6312,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="360" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:2">
       <c r="A360" t="s">
         <v>574</v>
       </c>
@@ -5926,7 +6320,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="361" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:2">
       <c r="A361" t="s">
         <v>575</v>
       </c>
@@ -5934,7 +6328,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="362" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:2">
       <c r="A362" t="s">
         <v>576</v>
       </c>
@@ -5942,7 +6336,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="363" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:2">
       <c r="A363" t="s">
         <v>577</v>
       </c>
@@ -5950,7 +6344,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="364" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:2">
       <c r="A364" t="s">
         <v>578</v>
       </c>
@@ -5958,7 +6352,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:2">
       <c r="A365" t="s">
         <v>579</v>
       </c>
@@ -5966,7 +6360,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:2">
       <c r="A366" t="s">
         <v>580</v>
       </c>
@@ -5974,7 +6368,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="367" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:2">
       <c r="A367" t="s">
         <v>581</v>
       </c>
@@ -5982,7 +6376,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="368" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:2">
       <c r="A368" t="s">
         <v>582</v>
       </c>
@@ -5990,7 +6384,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="369" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:2">
       <c r="A369" t="s">
         <v>583</v>
       </c>
@@ -5998,7 +6392,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="370" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:2">
       <c r="A370" t="s">
         <v>584</v>
       </c>
@@ -6006,7 +6400,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:2">
       <c r="A371" t="s">
         <v>585</v>
       </c>
@@ -6014,7 +6408,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:2">
       <c r="A372" t="s">
         <v>586</v>
       </c>
@@ -6022,7 +6416,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="373" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:2">
       <c r="A373" t="s">
         <v>587</v>
       </c>
@@ -6030,7 +6424,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:2">
       <c r="A374" t="s">
         <v>588</v>
       </c>
@@ -6038,7 +6432,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="375" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:2">
       <c r="A375" t="s">
         <v>589</v>
       </c>
@@ -6046,7 +6440,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:2">
       <c r="A376" t="s">
         <v>590</v>
       </c>
@@ -6054,7 +6448,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="377" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:2">
       <c r="A377" t="s">
         <v>591</v>
       </c>
@@ -6062,7 +6456,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="378" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:2">
       <c r="A378" t="s">
         <v>592</v>
       </c>
@@ -6070,7 +6464,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="379" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:2">
       <c r="A379" t="s">
         <v>593</v>
       </c>
@@ -6078,7 +6472,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="380" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:2">
       <c r="A380" t="s">
         <v>594</v>
       </c>
@@ -6086,7 +6480,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:2">
       <c r="A381" t="s">
         <v>595</v>
       </c>
@@ -6094,7 +6488,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="382" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:2">
       <c r="A382" t="s">
         <v>596</v>
       </c>
@@ -6102,7 +6496,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:2">
       <c r="A383" t="s">
         <v>597</v>
       </c>
@@ -6110,7 +6504,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:2">
       <c r="A384" t="s">
         <v>598</v>
       </c>
@@ -6118,7 +6512,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="385" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:2">
       <c r="A385" t="s">
         <v>599</v>
       </c>
@@ -6126,7 +6520,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="386" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:2">
       <c r="A386" t="s">
         <v>600</v>
       </c>
@@ -6134,7 +6528,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="387" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:2">
       <c r="A387" t="s">
         <v>601</v>
       </c>
@@ -6142,7 +6536,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="388" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:2">
       <c r="A388" t="s">
         <v>602</v>
       </c>
@@ -6150,7 +6544,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="389" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:2">
       <c r="A389" t="s">
         <v>603</v>
       </c>
@@ -6158,7 +6552,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="390" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:2">
       <c r="A390" t="s">
         <v>604</v>
       </c>
@@ -6166,7 +6560,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="391" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:2">
       <c r="A391" t="s">
         <v>605</v>
       </c>
@@ -6174,7 +6568,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="392" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:2">
       <c r="A392" t="s">
         <v>606</v>
       </c>
@@ -6182,7 +6576,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="393" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:2">
       <c r="A393" t="s">
         <v>607</v>
       </c>
@@ -6190,7 +6584,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="394" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:2">
       <c r="A394" t="s">
         <v>608</v>
       </c>
@@ -6198,7 +6592,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="395" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:2">
       <c r="A395" t="s">
         <v>609</v>
       </c>
@@ -6206,7 +6600,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="396" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:2">
       <c r="A396" t="s">
         <v>610</v>
       </c>
@@ -6214,7 +6608,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="397" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:2">
       <c r="A397" t="s">
         <v>611</v>
       </c>
@@ -6222,7 +6616,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="398" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:2">
       <c r="A398" t="s">
         <v>612</v>
       </c>
@@ -6230,7 +6624,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="399" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:2">
       <c r="A399" t="s">
         <v>613</v>
       </c>
@@ -6238,7 +6632,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="400" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:2">
       <c r="A400" t="s">
         <v>614</v>
       </c>
@@ -6246,7 +6640,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="401" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:2">
       <c r="A401" t="s">
         <v>615</v>
       </c>
@@ -6254,7 +6648,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="402" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:2">
       <c r="A402" t="s">
         <v>616</v>
       </c>
@@ -6262,7 +6656,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="403" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:2">
       <c r="A403" t="s">
         <v>617</v>
       </c>
@@ -6270,7 +6664,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="404" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:2">
       <c r="A404" t="s">
         <v>618</v>
       </c>
@@ -6278,7 +6672,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="405" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:2">
       <c r="A405" t="s">
         <v>619</v>
       </c>
@@ -6286,7 +6680,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="406" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:2">
       <c r="A406" t="s">
         <v>620</v>
       </c>
@@ -6294,7 +6688,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="407" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:2">
       <c r="A407" t="s">
         <v>621</v>
       </c>
@@ -6302,7 +6696,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="408" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:2">
       <c r="A408" t="s">
         <v>622</v>
       </c>
@@ -6310,7 +6704,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="409" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:2">
       <c r="A409" t="s">
         <v>623</v>
       </c>
@@ -6318,7 +6712,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="410" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:2">
       <c r="A410" t="s">
         <v>624</v>
       </c>
@@ -6326,7 +6720,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="411" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:2">
       <c r="A411" t="s">
         <v>625</v>
       </c>
@@ -6334,7 +6728,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="412" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:2">
       <c r="A412" t="s">
         <v>626</v>
       </c>
@@ -6342,7 +6736,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="413" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:2">
       <c r="A413" t="s">
         <v>627</v>
       </c>
@@ -6350,7 +6744,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="414" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:2">
       <c r="A414" t="s">
         <v>628</v>
       </c>
@@ -6358,7 +6752,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="415" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:2">
       <c r="A415" t="s">
         <v>629</v>
       </c>
@@ -6366,7 +6760,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="416" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:2">
       <c r="A416" t="s">
         <v>630</v>
       </c>
@@ -6374,7 +6768,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="417" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:2">
       <c r="A417" t="s">
         <v>631</v>
       </c>
@@ -6382,7 +6776,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="418" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:2">
       <c r="A418" t="s">
         <v>632</v>
       </c>
@@ -6390,7 +6784,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="419" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:2">
       <c r="A419" t="s">
         <v>633</v>
       </c>
@@ -6398,7 +6792,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="420" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:2">
       <c r="A420" t="s">
         <v>634</v>
       </c>
@@ -6406,7 +6800,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="421" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:2">
       <c r="A421" t="s">
         <v>635</v>
       </c>
@@ -6414,7 +6808,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="422" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:2">
       <c r="A422" t="s">
         <v>636</v>
       </c>
@@ -6422,7 +6816,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="423" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:2">
       <c r="A423" t="s">
         <v>637</v>
       </c>
@@ -6430,7 +6824,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="424" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:2">
       <c r="A424" t="s">
         <v>638</v>
       </c>
@@ -6438,7 +6832,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="425" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:2">
       <c r="A425" t="s">
         <v>639</v>
       </c>
@@ -6446,7 +6840,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="426" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:2">
       <c r="A426" t="s">
         <v>640</v>
       </c>
@@ -6454,7 +6848,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="427" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:2">
       <c r="A427" t="s">
         <v>641</v>
       </c>
@@ -6462,7 +6856,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="428" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:2">
       <c r="A428" t="s">
         <v>642</v>
       </c>
@@ -6470,7 +6864,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="429" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:2">
       <c r="A429" t="s">
         <v>643</v>
       </c>
@@ -6478,7 +6872,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="430" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:2">
       <c r="A430" t="s">
         <v>644</v>
       </c>
@@ -6486,7 +6880,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="431" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:2">
       <c r="A431" t="s">
         <v>645</v>
       </c>
@@ -6494,7 +6888,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="432" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:2">
       <c r="A432" t="s">
         <v>646</v>
       </c>
@@ -6502,7 +6896,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="433" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:2">
       <c r="A433" t="s">
         <v>647</v>
       </c>
@@ -6510,7 +6904,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="434" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:2">
       <c r="A434" t="s">
         <v>648</v>
       </c>
@@ -6518,7 +6912,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="435" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:2">
       <c r="A435" t="s">
         <v>882</v>
       </c>
@@ -6526,7 +6920,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="436" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:2">
       <c r="A436" t="s">
         <v>883</v>
       </c>
@@ -6534,7 +6928,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="437" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:2">
       <c r="A437" t="s">
         <v>884</v>
       </c>
@@ -6542,7 +6936,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="438" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:2">
       <c r="A438" t="s">
         <v>885</v>
       </c>
@@ -6550,7 +6944,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="439" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:2">
       <c r="A439" t="s">
         <v>886</v>
       </c>
@@ -6558,7 +6952,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="440" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:2">
       <c r="A440" t="s">
         <v>887</v>
       </c>
@@ -6566,7 +6960,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="441" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:2">
       <c r="A441" t="s">
         <v>888</v>
       </c>
@@ -6574,7 +6968,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="442" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:2">
       <c r="A442" t="s">
         <v>889</v>
       </c>
@@ -6582,7 +6976,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="443" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:2">
       <c r="A443" t="s">
         <v>890</v>
       </c>
@@ -6590,7 +6984,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="444" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:2">
       <c r="A444" t="s">
         <v>891</v>
       </c>
@@ -6598,7 +6992,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="445" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:2">
       <c r="A445" t="s">
         <v>892</v>
       </c>
@@ -6606,7 +7000,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="446" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:2">
       <c r="A446" t="s">
         <v>893</v>
       </c>
@@ -6614,7 +7008,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="447" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:2">
       <c r="A447" t="s">
         <v>894</v>
       </c>
@@ -6622,12 +7016,464 @@
         <v>874</v>
       </c>
     </row>
-    <row r="448" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:2">
       <c r="A448" t="s">
         <v>895</v>
       </c>
       <c r="B448" t="s">
         <v>881</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DC3A44B-0D44-42A7-8178-D5849C0E92B0}">
+  <dimension ref="A1:T24"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20">
+      <c r="A1" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>954</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>985</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20">
+      <c r="A2" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="A3" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>963</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="A4" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>953</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>986</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>995</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="A5" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>933</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>965</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="A6" s="1" t="s">
+        <v>907</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>966</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="A7" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>935</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="A8" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="A9" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>969</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="A10" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>926</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>938</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>970</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>991</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>1001</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="A11" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>939</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>971</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="A12" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>940</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>972</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="A13" s="1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>941</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>956</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>973</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>987</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="A14" s="1" t="s">
+        <v>914</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="A15" s="1" t="s">
+        <v>913</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="A16" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="T16" s="2" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20">
+      <c r="A17" s="1" t="s">
+        <v>912</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>945</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="S17" s="1" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20">
+      <c r="A18" s="1" t="s">
+        <v>915</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>978</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20">
+      <c r="A19" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>979</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="T19" s="2" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20">
+      <c r="A20" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>948</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20">
+      <c r="A21" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>949</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20">
+      <c r="A22" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>950</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>958</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>982</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="T22" s="2" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20">
+      <c r="A23" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>951</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="S23" s="1" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20">
+      <c r="A24" s="1" t="s">
+        <v>919</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>952</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>1015</v>
       </c>
     </row>
   </sheetData>
